--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="101 Kings Road 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="101 Kings Road" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12260,163 +12298,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>101 Kings Road - 101 Kings Road 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>101 Kings Road 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>251 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>243 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1291呎 (4+房)
 招标单位
@@ -12424,15 +12462,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 877呎 (3房)
-$4,210万
+$4210万
 $48,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 1119呎 (3房)
 招标单位
@@ -12440,29 +12478,29 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 861呎 (3房)
-$4,133万
+$4133万
 $48,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 招标单位
@@ -12470,8 +12508,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 招标单位
@@ -12479,15 +12517,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,471万
+$1471万
 $33,441/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $972万
@@ -12495,7 +12533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $655万
@@ -12503,7 +12541,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $967万
@@ -12511,15 +12549,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,050万
+$1050万
 $24,294/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $648万
@@ -12527,55 +12565,55 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,064万
+$1064万
 $28,298/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,187万
+$1187万
 $27,357/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-$3,101万
+$3101万
 $37,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,913万
+$1913万
 $33,680/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,459万
+$1459万
 $33,150/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $956万
@@ -12583,7 +12621,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $646万
@@ -12591,7 +12629,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $928万
@@ -12599,15 +12637,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,037万
+$1037万
 $23,998/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $640万
@@ -12615,55 +12653,55 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,054万
+$1054万
 $28,021/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,226万
+$1226万
 $28,256/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-$3,017万
+$3017万
 $36,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,851万
+$1851万
 $32,590/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,446万
+$1446万
 $32,859/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $940万
@@ -12671,7 +12709,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $644万
@@ -12679,7 +12717,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $924万
@@ -12687,15 +12725,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,034万
+$1034万
 $23,942/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $632万
@@ -12703,55 +12741,55 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,043万
+$1043万
 $27,745/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,164万
+$1164万
 $26,832/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-$2,944万
+$2944万
 $35,135/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,750万
+$1750万
 $30,817/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,433万
+$1433万
 $32,570/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $926万
@@ -12759,7 +12797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $634万
@@ -12767,7 +12805,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $912万
@@ -12775,15 +12813,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,017万
+$1017万
 $23,535/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $642万
@@ -12791,55 +12829,55 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,033万
+$1033万
 $27,471/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,153万
+$1153万
 $26,567/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-$2,933万
+$2933万
 $35,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,743万
+$1743万
 $30,680/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,480万
+$1480万
 $33,627/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $912万
@@ -12847,7 +12885,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $625万
@@ -12855,7 +12893,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $899万
@@ -12863,15 +12901,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,028万
+$1028万
 $23,789/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $634万
@@ -12879,55 +12917,55 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,008万
+$1008万
 $26,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,142万
+$1142万
 $26,304/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-$2,430万
+$2430万
 $29,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,704万
+$1704万
 $30,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,409万
+$1409万
 $32,030/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $898万
@@ -12935,7 +12973,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $599万
@@ -12943,7 +12981,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $886万
@@ -12951,15 +12989,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,010万
+$1010万
 $23,368/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $627万
@@ -12967,38 +13005,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,012万
+$1012万
 $26,918/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,130万
+$1130万
 $26,041/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,653万
+$1653万
 $30,104/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $866万
@@ -13006,23 +13044,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,669万
+$1669万
 $29,380/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,512万
+$1512万
 $34,368/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $885万
@@ -13030,7 +13068,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $607万
@@ -13038,7 +13076,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $898万
@@ -13046,7 +13084,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $964万
@@ -13054,7 +13092,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $619万
@@ -13062,38 +13100,38 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
-$1,002万
+$1002万
 $26,644/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,119万
+$1119万
 $25,779/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,637万
+$1637万
 $29,816/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $857万
@@ -13101,23 +13139,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,636万
+$1636万
 $28,799/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,902万
+$1902万
 $43,218/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $903万
@@ -13125,7 +13163,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $584万
@@ -13133,7 +13171,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $888万
@@ -13141,7 +13179,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $956万
@@ -13149,7 +13187,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $594万
@@ -13157,7 +13195,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $951万
@@ -13165,30 +13203,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,108万
+$1108万
 $25,535/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,584万
+$1584万
 $28,852/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $847万
@@ -13196,23 +13234,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,590万
+$1590万
 $28,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,422万
+$1422万
 $32,318/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $871万
@@ -13220,7 +13258,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $595万
@@ -13228,7 +13266,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $877万
@@ -13236,7 +13274,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $975万
@@ -13244,7 +13282,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $605万
@@ -13252,7 +13290,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $941万
@@ -13260,30 +13298,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,129万
+$1129万
 $26,012/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,618万
+$1618万
 $29,466/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $837万
@@ -13291,23 +13329,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,565万
+$1565万
 $27,560/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,343万
+$1343万
 $30,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $889万
@@ -13315,7 +13353,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $573万
@@ -13323,7 +13361,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $867万
@@ -13331,7 +13369,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $966万
@@ -13339,7 +13377,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $599万
@@ -13347,7 +13385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $958万
@@ -13355,30 +13393,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,087万
+$1087万
 $25,041/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,583万
+$1583万
 $28,842/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $828万
@@ -13386,23 +13424,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,535万
+$1535万
 $27,019/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,321万
+$1321万
 $30,020/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $858万
@@ -13410,7 +13448,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $584万
@@ -13418,7 +13456,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $856万
@@ -13426,7 +13464,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $958万
@@ -13434,7 +13472,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $593万
@@ -13442,7 +13480,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $948万
@@ -13450,30 +13488,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,107万
+$1107万
 $25,505/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,546万
+$1546万
 $28,157/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $784万
@@ -13481,23 +13519,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,592万
+$1592万
 $28,032/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,298万
+$1298万
 $29,509/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $851万
@@ -13505,7 +13543,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $578万
@@ -13513,7 +13551,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $846万
@@ -13521,7 +13559,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $923万
@@ -13529,7 +13567,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $592万
@@ -13537,7 +13575,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $913万
@@ -13545,30 +13583,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,096万
+$1096万
 $25,249/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,452万
+$1452万
 $26,455/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $808万
@@ -13576,23 +13614,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,500万
+$1500万
 $26,400/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,285万
+$1285万
 $29,200/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $845万
@@ -13600,7 +13638,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $572万
@@ -13608,7 +13646,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $835万
@@ -13616,15 +13654,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,255万
+$1255万
 $29,058/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $586万
@@ -13632,7 +13670,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $903万
@@ -13640,30 +13678,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,055万
+$1055万
 $24,302/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,439万
+$1439万
 $26,208/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $766万
@@ -13671,23 +13709,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,465万
+$1465万
 $25,799/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,276万
+$1276万
 $28,991/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $838万
@@ -13695,7 +13733,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $566万
@@ -13703,7 +13741,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $802万
@@ -13711,7 +13749,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $907万
@@ -13719,7 +13757,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $580万
@@ -13727,7 +13765,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $893万
@@ -13735,30 +13773,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,074万
+$1074万
 $24,747/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,414万
+$1414万
 $25,754/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $782万
@@ -13766,23 +13804,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,447万
+$1447万
 $25,474/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,266万
+$1266万
 $28,780/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $852万
@@ -13790,7 +13828,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $544万
@@ -13798,7 +13836,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $818万
@@ -13806,7 +13844,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $925万
@@ -13814,7 +13852,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $575万
@@ -13822,7 +13860,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $912万
@@ -13830,30 +13868,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,066万
+$1066万
 $24,553/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,400万
+$1400万
 $25,508/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $753万
@@ -13861,23 +13899,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,445万
+$1445万
 $25,438/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,257万
+$1257万
 $28,570/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $841万
@@ -13885,7 +13923,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $553万
@@ -13893,7 +13931,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $811万
@@ -13901,7 +13939,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $917万
@@ -13909,7 +13947,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $570万
@@ -13917,7 +13955,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $914万
@@ -13925,30 +13963,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,068万
+$1068万
 $24,608/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,446万
+$1446万
 $26,344/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $748万
@@ -13956,23 +13994,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,387万
+$1387万
 $24,417/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,248万
+$1248万
 $28,359/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $808万
@@ -13980,7 +14018,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $547万
@@ -13988,7 +14026,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $781万
@@ -13996,7 +14034,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $908万
@@ -14004,7 +14042,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $566万
@@ -14012,7 +14050,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $881万
@@ -14020,30 +14058,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,060万
+$1060万
 $24,419/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,373万
+$1373万
 $25,016/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $744万
@@ -14051,23 +14089,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,373万
+$1373万
 $24,180/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,239万
+$1239万
 $28,150/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $798万
@@ -14075,7 +14113,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $540万
@@ -14083,7 +14121,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $797万
@@ -14091,15 +14129,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
-$1,113万
+$1113万
 $25,759/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $562万
@@ -14107,7 +14145,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $874万
@@ -14115,30 +14153,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,051万
+$1051万
 $24,226/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,418万
+$1418万
 $25,832/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $735万
@@ -14146,23 +14184,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,632万
+$1632万
 $28,731/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,229万
+$1229万
 $27,941/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $810万
@@ -14170,7 +14208,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $519万
@@ -14178,7 +14216,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $768万
@@ -14186,7 +14224,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $867万
@@ -14194,7 +14232,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $557万
@@ -14202,7 +14240,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $867万
@@ -14210,30 +14248,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,043万
+$1043万
 $24,035/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,346万
+$1346万
 $24,525/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $727万
@@ -14241,23 +14279,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,346万
+$1346万
 $23,704/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,220万
+$1220万
 $27,730/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $777万
@@ -14265,7 +14303,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $528万
@@ -14273,7 +14311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $783万
@@ -14281,7 +14319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $884万
@@ -14289,7 +14327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $553万
@@ -14297,7 +14335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $885万
@@ -14305,30 +14343,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,035万
+$1035万
 $23,841/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,333万
+$1333万
 $24,279/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $718万
@@ -14336,23 +14374,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,333万
+$1333万
 $23,467/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,211万
+$1211万
 $27,520/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $789万
@@ -14360,7 +14398,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $521万
@@ -14368,7 +14406,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $776万
@@ -14376,7 +14414,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $876万
@@ -14384,7 +14422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $533万
@@ -14392,7 +14430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $853万
@@ -14400,30 +14438,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,026万
+$1026万
 $23,650/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
-$1,333万
+$1333万
 $24,286/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $710万
@@ -14431,23 +14469,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-$1,328万
+$1328万
 $23,387/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,174万
+$1174万
 $26,680/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $775万
@@ -14455,7 +14493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $502万
@@ -14463,7 +14501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $769万
@@ -14471,7 +14509,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $863万
@@ -14479,7 +14517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $544万
@@ -14487,7 +14525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K28" s="17" t="inlineStr">
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $846万
@@ -14495,30 +14533,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
-$1,018万
+$1018万
 $23,459/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$2,150万
+$2150万
 $42,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 273呎 (1房)
 招标单位
@@ -14526,7 +14564,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
 招标单位
@@ -14534,7 +14572,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 402呎 (2房)
 招标单位
@@ -14542,15 +14580,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 358呎 (2房)
-$1,432万
+$1432万
 $40,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 225呎 (1房)
 $880万
@@ -14558,23 +14596,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 343呎 (2房)
-$1,374万
+$1374万
 $40,058/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 394呎 (2房)
-$1,734万
+$1734万
 $44,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J29" s="17" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 204呎 (1房)
 $857万
@@ -14582,18 +14620,18 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K29" s="17" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
         <is>
           <t>K | 340呎 (2房)
-$1,360万
+$1360万
 $40,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>L | 397呎 (2房)
-$1,628万
+$1628万
 $41,000/呎
 (已售)</t>
         </is>
@@ -14601,7 +14639,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
